--- a/entertainment_forms/020_new_year_quiz--entertainment_forms.xlsx
+++ b/entertainment_forms/020_new_year_quiz--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>welcome</t>
+          <t>current_goals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Welcome</t>
+          <t>What are your current goals?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +543,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>favorite_places</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Where do you spend most of your free time?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>hobbies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>What are your favorite activities or hobbies?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>vacation_last_year</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>When</t>
+          <t>Where did you go on a vacation last year?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>best_time_of_year</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which</t>
+          <t>What is the best time of year for you?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>favorite_entertainment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>What is your favorite type of entertainment?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>favorite_music</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>What is your favorite type of music?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>movie_watching_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>How often do you go to the movies?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,384 +704,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>favorite_restaurant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Do you have a favorite restaurant?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,610 +758,1137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>short-term_goals</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Short-term goals</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>goals_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>long-term_goals</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Long-term goals</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>personal_goals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Personal goals</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>career_goals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Career goals</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>financial_goals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Financial goals</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>education_goals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Education goals</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>health_and_wellness_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Health and wellness goals</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>relationship_goals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Relationship goals</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>travel_goals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Travel goals</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>current_goals_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hobbies_goals</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hobbies goals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>School</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>forest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>favorite_places_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rural_area</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rural area</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cooking</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Playing video games</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>hobbies_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>beach_resort</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Beach resort</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>city_break</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>City break</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>national_park</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>National park</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>theme_park</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Theme park</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cruise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Cruise</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_23_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cruise_ship</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cruise ship</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_23_choices</t>
+          <t>vacation_last_year_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>road_trip</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Road trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>vacation_last_year_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hiking</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hiking</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>vacation_last_year_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mountain_retreat</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mountain retreat</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>vacation_last_year_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>best_time_of_year_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>best_time_of_year_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>summer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>best_time_of_year_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>autumn</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>best_time_of_year_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tv_shows</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TV shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>movies</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Movies</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>video_games</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Video games</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>books</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>theater</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>concerts</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Concerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>favorite_entertainment_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>festivals</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Festivals</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>rock</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>classical</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Classical</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>jazz</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Jazz</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>folk</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Folk</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>hip-hop</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hip-hop</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>electronic</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Electronic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>favorite_music_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>r&amp;b</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>R&amp;B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>movie_watching_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>movie_watching_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>movie_watching_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>movie_watching_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>favorite_restaurant_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>favorite_restaurant_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>No</t>
         </is>
